--- a/backtest_runs/20260410_193731/by_symbol/TSMF/TSMF.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/TSMF/TSMF.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         <v>-10660.44</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>94851.07999999999</v>
@@ -817,7 +817,7 @@
         <v>-2973.320000000001</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>91877.75999999999</v>
@@ -863,7 +863,7 @@
         <v>-362.5999999999923</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>91515.16</v>
@@ -1001,7 +1001,7 @@
         <v>-4278.679999999999</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>87236.48</v>
@@ -1139,7 +1139,7 @@
         <v>-580.1600000000005</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>86656.32000000001</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>86656.32000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-5439</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>94706.03999999999</v>
@@ -1415,7 +1415,7 @@
         <v>-435.1200000000036</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>94270.92</v>
